--- a/data/schedule.xlsx
+++ b/data/schedule.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,56 +441,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>🔥 MSI G2712F 27" FHD 180Hz — chỉ 1.600.000đ. Ib mình nhé!</t>
+          <t>MSI G274QPF E2 27" 2K 180Hz — 2.600.000đ. Hàng đẹp, bảo hành đầy đủ!</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MSI_G2712F_FHD_180Hz_Gia_1600000d.jpg</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>MSI_G274QPF_E2_2K_180Hz_Gia_2400000d.png</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MSI G274QPF E2 27" 2K 180Hz — 2.400.000đ. Hàng đẹp, bảo hành đầy đủ!</t>
+          <t>MSI G274QRFW 27" 2K 170Hz màu trắng — 2.650.000đ. Ib để được tư vấn!</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MSI_G274QPF_E2_2K_180Hz_Gia_2400000d.png</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>MSI G274QRFW 27" 2K 170Hz màu trắng — 2.450.000đ. Ib để được tư vấn!</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
           <t>MSI_G274QRFW_2K_170Hz_Gia_2450000d.png</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
